--- a/outputs/Maize_tukey_classification_matrix.xlsx
+++ b/outputs/Maize_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5280" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5280" uniqueCount="271">
   <si>
     <t>2008 Jan</t>
   </si>
@@ -746,6 +746,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alarm</t>
@@ -1999,7 +2002,7 @@
         <v>243</v>
       </c>
       <c r="AR2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AS2" t="s">
         <v>243</v>
@@ -2206,13 +2209,13 @@
         <v>243</v>
       </c>
       <c r="DI2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DJ2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL2" t="s">
         <v>243</v>
@@ -2386,79 +2389,79 @@
         <v>243</v>
       </c>
       <c r="FQ2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FR2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FS2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GP2" t="s">
         <v>243</v>
@@ -2485,49 +2488,49 @@
         <v>243</v>
       </c>
       <c r="GX2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HG2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HH2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HI2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HJ2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="HK2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="HL2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:220">
@@ -2661,7 +2664,7 @@
         <v>243</v>
       </c>
       <c r="AR3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AS3" t="s">
         <v>243</v>
@@ -2862,31 +2865,31 @@
         <v>243</v>
       </c>
       <c r="DG3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DH3" t="s">
         <v>243</v>
       </c>
       <c r="DI3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM3" t="s">
         <v>243</v>
       </c>
       <c r="DN3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DO3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DP3" t="s">
         <v>243</v>
@@ -2955,7 +2958,7 @@
         <v>243</v>
       </c>
       <c r="EL3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EM3" t="s">
         <v>243</v>
@@ -3051,67 +3054,67 @@
         <v>243</v>
       </c>
       <c r="FR3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM3" t="s">
         <v>243</v>
@@ -3144,52 +3147,52 @@
         <v>243</v>
       </c>
       <c r="GW3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GX3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HD3" t="s">
         <v>243</v>
       </c>
       <c r="HE3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH3" t="s">
         <v>243</v>
       </c>
       <c r="HI3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HJ3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="HK3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:220">
@@ -3338,7 +3341,7 @@
         <v>243</v>
       </c>
       <c r="AW4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AX4" t="s">
         <v>243</v>
@@ -3683,22 +3686,22 @@
         <v>243</v>
       </c>
       <c r="FH4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FI4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FJ4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FK4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FL4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FM4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FN4" t="s">
         <v>243</v>
@@ -3713,145 +3716,145 @@
         <v>243</v>
       </c>
       <c r="FR4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FS4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GP4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GQ4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GR4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GS4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GT4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GU4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GV4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GW4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GX4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="HK4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="HL4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:220">
@@ -4378,67 +4381,67 @@
         <v>243</v>
       </c>
       <c r="FS5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN5" t="s">
         <v>243</v>
@@ -4474,22 +4477,22 @@
         <v>243</v>
       </c>
       <c r="GY5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GZ5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HA5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HB5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE5" t="s">
         <v>243</v>
@@ -4501,19 +4504,19 @@
         <v>243</v>
       </c>
       <c r="HH5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="HK5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="HL5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:220">
@@ -4674,10 +4677,10 @@
         <v>243</v>
       </c>
       <c r="BA6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="BB6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="BC6" t="s">
         <v>243</v>
@@ -4686,7 +4689,7 @@
         <v>243</v>
       </c>
       <c r="BE6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="BF6" t="s">
         <v>243</v>
@@ -4854,10 +4857,10 @@
         <v>243</v>
       </c>
       <c r="DI6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DJ6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DK6" t="s">
         <v>243</v>
@@ -4866,16 +4869,16 @@
         <v>243</v>
       </c>
       <c r="DM6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DN6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DO6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DP6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DQ6" t="s">
         <v>243</v>
@@ -5040,73 +5043,73 @@
         <v>243</v>
       </c>
       <c r="FS6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FT6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GP6" t="s">
         <v>243</v>
@@ -5124,58 +5127,58 @@
         <v>243</v>
       </c>
       <c r="GU6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GV6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GW6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GX6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GY6" t="s">
         <v>243</v>
       </c>
       <c r="GZ6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HA6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="HK6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="HL6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:220">
@@ -5516,16 +5519,16 @@
         <v>243</v>
       </c>
       <c r="DI7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK7" t="s">
         <v>243</v>
       </c>
       <c r="DL7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DM7" t="s">
         <v>243</v>
@@ -5537,7 +5540,7 @@
         <v>243</v>
       </c>
       <c r="DP7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DQ7" t="s">
         <v>243</v>
@@ -5702,73 +5705,73 @@
         <v>243</v>
       </c>
       <c r="FS7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV7" t="s">
         <v>243</v>
       </c>
       <c r="FW7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN7" t="s">
         <v>243</v>
       </c>
       <c r="GO7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GP7" t="s">
         <v>243</v>
@@ -5795,34 +5798,34 @@
         <v>243</v>
       </c>
       <c r="GX7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HD7" t="s">
         <v>243</v>
       </c>
       <c r="HE7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF7" t="s">
         <v>243</v>
       </c>
       <c r="HG7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HH7" t="s">
         <v>243</v>
@@ -5831,13 +5834,13 @@
         <v>243</v>
       </c>
       <c r="HJ7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="HK7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="HL7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:220">
@@ -6172,22 +6175,22 @@
         <v>243</v>
       </c>
       <c r="DG8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DH8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DI8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM8" t="s">
         <v>243</v>
@@ -6358,73 +6361,73 @@
         <v>243</v>
       </c>
       <c r="FQ8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FR8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN8" t="s">
         <v>243</v>
@@ -6454,52 +6457,52 @@
         <v>243</v>
       </c>
       <c r="GW8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GX8" t="s">
         <v>243</v>
       </c>
       <c r="GY8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GZ8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="HK8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:220">
@@ -6840,16 +6843,16 @@
         <v>243</v>
       </c>
       <c r="DI9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM9" t="s">
         <v>243</v>
@@ -7023,70 +7026,70 @@
         <v>243</v>
       </c>
       <c r="FR9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FS9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK9" t="s">
         <v>243</v>
       </c>
       <c r="GL9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GN9" t="s">
         <v>243</v>
@@ -7116,28 +7119,28 @@
         <v>243</v>
       </c>
       <c r="GW9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GX9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE9" t="s">
         <v>243</v>
@@ -7152,16 +7155,16 @@
         <v>243</v>
       </c>
       <c r="HI9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HJ9" t="s">
+        <v>252</v>
+      </c>
+      <c r="HK9" t="s">
+        <v>263</v>
+      </c>
+      <c r="HL9" t="s">
         <v>251</v>
-      </c>
-      <c r="HK9" t="s">
-        <v>262</v>
-      </c>
-      <c r="HL9" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:220">
@@ -7289,22 +7292,22 @@
         <v>243</v>
       </c>
       <c r="AP10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AQ10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AR10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AS10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AT10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AU10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AV10" t="s">
         <v>243</v>
@@ -7502,19 +7505,19 @@
         <v>243</v>
       </c>
       <c r="DI10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DN10" t="s">
         <v>243</v>
@@ -7682,73 +7685,73 @@
         <v>243</v>
       </c>
       <c r="FQ10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FR10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN10" t="s">
         <v>243</v>
@@ -7793,16 +7796,16 @@
         <v>243</v>
       </c>
       <c r="HB10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HC10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HF10" t="s">
         <v>243</v>
@@ -7817,13 +7820,13 @@
         <v>243</v>
       </c>
       <c r="HJ10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="HK10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="HL10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:220">
@@ -7831,7 +7834,7 @@
         <v>229</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
         <v>243</v>
@@ -7960,7 +7963,7 @@
         <v>243</v>
       </c>
       <c r="AS11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AT11" t="s">
         <v>243</v>
@@ -8167,13 +8170,13 @@
         <v>243</v>
       </c>
       <c r="DJ11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DK11" t="s">
         <v>243</v>
       </c>
       <c r="DL11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM11" t="s">
         <v>243</v>
@@ -8212,7 +8215,7 @@
         <v>243</v>
       </c>
       <c r="DY11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DZ11" t="s">
         <v>243</v>
@@ -8227,19 +8230,19 @@
         <v>243</v>
       </c>
       <c r="ED11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EE11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EF11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EG11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EH11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EI11" t="s">
         <v>243</v>
@@ -8248,37 +8251,37 @@
         <v>243</v>
       </c>
       <c r="EK11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EL11" t="s">
         <v>243</v>
       </c>
       <c r="EM11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EN11" t="s">
         <v>243</v>
       </c>
       <c r="EO11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EP11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EQ11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="ER11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="ES11" t="s">
         <v>243</v>
       </c>
       <c r="ET11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EU11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EV11" t="s">
         <v>243</v>
@@ -8332,7 +8335,7 @@
         <v>243</v>
       </c>
       <c r="FM11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FN11" t="s">
         <v>243</v>
@@ -8353,139 +8356,139 @@
         <v>243</v>
       </c>
       <c r="FT11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FU11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GP11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GQ11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GR11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GS11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GT11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GU11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GV11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GW11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GX11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="HK11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="HL11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:220">
@@ -8823,22 +8826,22 @@
         <v>243</v>
       </c>
       <c r="DH12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DI12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DN12" t="s">
         <v>243</v>
@@ -9006,79 +9009,79 @@
         <v>243</v>
       </c>
       <c r="FQ12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FR12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GP12" t="s">
         <v>243</v>
@@ -9108,46 +9111,46 @@
         <v>243</v>
       </c>
       <c r="GY12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GZ12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="HK12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:220">
@@ -9662,7 +9665,7 @@
         <v>243</v>
       </c>
       <c r="FO13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FP13" t="s">
         <v>243</v>
@@ -9674,67 +9677,67 @@
         <v>243</v>
       </c>
       <c r="FS13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FT13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FU13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FV13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GE13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GF13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GG13" t="s">
         <v>243</v>
       </c>
       <c r="GH13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN13" t="s">
         <v>243</v>
@@ -9743,73 +9746,73 @@
         <v>243</v>
       </c>
       <c r="GP13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GQ13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GR13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GS13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GT13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GU13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GV13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GW13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GX13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HG13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI13" t="s">
         <v>243</v>
       </c>
       <c r="HJ13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="HK13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="HL13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:220">
@@ -10333,88 +10336,88 @@
         <v>243</v>
       </c>
       <c r="FR14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FS14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GO14" t="s">
         <v>243</v>
       </c>
       <c r="GP14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GQ14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GR14" t="s">
         <v>243</v>
       </c>
       <c r="GS14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GT14" t="s">
         <v>243</v>
@@ -10426,25 +10429,25 @@
         <v>243</v>
       </c>
       <c r="GW14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GX14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HA14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HD14" t="s">
         <v>243</v>
@@ -10456,22 +10459,22 @@
         <v>243</v>
       </c>
       <c r="HG14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="HK14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:220">
@@ -10605,22 +10608,22 @@
         <v>243</v>
       </c>
       <c r="AR15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AS15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AT15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AU15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AV15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AW15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AX15" t="s">
         <v>243</v>
@@ -10806,31 +10809,31 @@
         <v>243</v>
       </c>
       <c r="DG15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DH15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DI15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DN15" t="s">
         <v>243</v>
       </c>
       <c r="DO15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DP15" t="s">
         <v>243</v>
@@ -10845,7 +10848,7 @@
         <v>243</v>
       </c>
       <c r="DT15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DU15" t="s">
         <v>243</v>
@@ -10899,13 +10902,13 @@
         <v>243</v>
       </c>
       <c r="EL15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EM15" t="s">
         <v>243</v>
       </c>
       <c r="EN15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EO15" t="s">
         <v>243</v>
@@ -10989,76 +10992,76 @@
         <v>243</v>
       </c>
       <c r="FP15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FQ15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FR15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GN15" t="s">
         <v>243</v>
@@ -11088,52 +11091,52 @@
         <v>243</v>
       </c>
       <c r="GW15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GX15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE15" t="s">
         <v>243</v>
       </c>
       <c r="HF15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HG15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="HK15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="HL15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:220">
@@ -11243,10 +11246,10 @@
         <v>243</v>
       </c>
       <c r="AJ16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AK16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL16" t="s">
         <v>243</v>
@@ -11267,344 +11270,344 @@
         <v>243</v>
       </c>
       <c r="AR16" t="s">
+        <v>245</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>245</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>245</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>245</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>245</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>245</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>245</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BO16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BP16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BQ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BS16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BT16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BU16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BV16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BW16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BX16" t="s">
+        <v>246</v>
+      </c>
+      <c r="BY16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BZ16" t="s">
+        <v>246</v>
+      </c>
+      <c r="CA16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CC16" t="s">
+        <v>246</v>
+      </c>
+      <c r="CD16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CE16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CF16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CI16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CJ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CK16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CL16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CM16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CN16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CO16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CP16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CQ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CR16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CS16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CT16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CU16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CV16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CW16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CX16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CY16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CZ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DA16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DB16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DC16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DD16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DE16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DF16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DG16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DH16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DI16" t="s">
+        <v>245</v>
+      </c>
+      <c r="DJ16" t="s">
+        <v>245</v>
+      </c>
+      <c r="DK16" t="s">
+        <v>245</v>
+      </c>
+      <c r="DL16" t="s">
+        <v>245</v>
+      </c>
+      <c r="DM16" t="s">
+        <v>246</v>
+      </c>
+      <c r="DN16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DO16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DP16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DQ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DR16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DS16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DT16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DU16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DV16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DW16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DX16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DY16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DZ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EA16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EB16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EC16" t="s">
+        <v>243</v>
+      </c>
+      <c r="ED16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EE16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EF16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EG16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EH16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EJ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EK16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EL16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EM16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EN16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EO16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EP16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EQ16" t="s">
+        <v>243</v>
+      </c>
+      <c r="ER16" t="s">
+        <v>243</v>
+      </c>
+      <c r="ES16" t="s">
+        <v>243</v>
+      </c>
+      <c r="ET16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EU16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EV16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EW16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EX16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EY16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EZ16" t="s">
         <v>244</v>
       </c>
-      <c r="AS16" t="s">
-        <v>244</v>
-      </c>
-      <c r="AT16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AU16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AW16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AY16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AZ16" t="s">
-        <v>244</v>
-      </c>
-      <c r="BA16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BB16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BC16" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD16" t="s">
-        <v>244</v>
-      </c>
-      <c r="BE16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BF16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BG16" t="s">
-        <v>244</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>244</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BJ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BK16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BL16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BM16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BN16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BP16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BQ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BR16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BS16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BT16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BU16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BV16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BW16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BX16" t="s">
-        <v>245</v>
-      </c>
-      <c r="BY16" t="s">
-        <v>243</v>
-      </c>
-      <c r="BZ16" t="s">
-        <v>245</v>
-      </c>
-      <c r="CA16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CC16" t="s">
-        <v>245</v>
-      </c>
-      <c r="CD16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CE16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CF16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CG16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CH16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CI16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CJ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CK16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CL16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CM16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CN16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CO16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CP16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CQ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CR16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CS16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CT16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CU16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CV16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CW16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CX16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CY16" t="s">
-        <v>243</v>
-      </c>
-      <c r="CZ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DA16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DB16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DC16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DD16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DE16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DF16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DG16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DH16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DI16" t="s">
-        <v>244</v>
-      </c>
-      <c r="DJ16" t="s">
-        <v>244</v>
-      </c>
-      <c r="DK16" t="s">
-        <v>244</v>
-      </c>
-      <c r="DL16" t="s">
-        <v>244</v>
-      </c>
-      <c r="DM16" t="s">
-        <v>245</v>
-      </c>
-      <c r="DN16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DO16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DP16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DQ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DR16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DS16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DT16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DU16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DV16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DW16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DX16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DY16" t="s">
-        <v>243</v>
-      </c>
-      <c r="DZ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EA16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EB16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EC16" t="s">
-        <v>243</v>
-      </c>
-      <c r="ED16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EE16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EF16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EG16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EH16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EI16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EJ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EK16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EL16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EM16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EN16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EO16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EP16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EQ16" t="s">
-        <v>243</v>
-      </c>
-      <c r="ER16" t="s">
-        <v>243</v>
-      </c>
-      <c r="ES16" t="s">
-        <v>243</v>
-      </c>
-      <c r="ET16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EU16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EV16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EW16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EX16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EY16" t="s">
-        <v>243</v>
-      </c>
-      <c r="EZ16" t="s">
-        <v>243</v>
-      </c>
       <c r="FA16" t="s">
         <v>243</v>
       </c>
@@ -11660,55 +11663,55 @@
         <v>243</v>
       </c>
       <c r="FS16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH16" t="s">
         <v>243</v>
       </c>
       <c r="GI16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ16" t="s">
         <v>243</v>
@@ -11753,28 +11756,28 @@
         <v>243</v>
       </c>
       <c r="GX16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY16" t="s">
         <v>243</v>
       </c>
       <c r="GZ16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HA16" t="s">
         <v>243</v>
       </c>
       <c r="HB16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF16" t="s">
         <v>243</v>
@@ -11789,13 +11792,13 @@
         <v>243</v>
       </c>
       <c r="HJ16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="HK16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:220">
@@ -12151,7 +12154,7 @@
         <v>243</v>
       </c>
       <c r="DN17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DO17" t="s">
         <v>243</v>
@@ -12163,7 +12166,7 @@
         <v>243</v>
       </c>
       <c r="DR17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DS17" t="s">
         <v>243</v>
@@ -12322,67 +12325,67 @@
         <v>243</v>
       </c>
       <c r="FS17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN17" t="s">
         <v>243</v>
@@ -12421,28 +12424,28 @@
         <v>243</v>
       </c>
       <c r="GZ17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HA17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HB17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HC17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HD17" t="s">
         <v>243</v>
       </c>
       <c r="HE17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HF17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HG17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HH17" t="s">
         <v>243</v>
@@ -12451,13 +12454,13 @@
         <v>243</v>
       </c>
       <c r="HJ17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="HK17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="HL17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:220">
@@ -12528,13 +12531,13 @@
         <v>243</v>
       </c>
       <c r="W18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Y18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z18" t="s">
         <v>243</v>
@@ -12594,7 +12597,7 @@
         <v>243</v>
       </c>
       <c r="AS18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AT18" t="s">
         <v>243</v>
@@ -12801,7 +12804,7 @@
         <v>243</v>
       </c>
       <c r="DJ18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK18" t="s">
         <v>243</v>
@@ -12984,73 +12987,73 @@
         <v>243</v>
       </c>
       <c r="FS18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GP18" t="s">
         <v>243</v>
@@ -13092,13 +13095,13 @@
         <v>243</v>
       </c>
       <c r="HC18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HD18" t="s">
         <v>243</v>
       </c>
       <c r="HE18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HF18" t="s">
         <v>243</v>
@@ -13113,13 +13116,13 @@
         <v>243</v>
       </c>
       <c r="HJ18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="HK18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:220">
@@ -13643,67 +13646,67 @@
         <v>243</v>
       </c>
       <c r="FR19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM19" t="s">
         <v>243</v>
@@ -13742,46 +13745,46 @@
         <v>243</v>
       </c>
       <c r="GY19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HI19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HJ19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="HK19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="HL19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:220">
@@ -14188,7 +14191,7 @@
         <v>243</v>
       </c>
       <c r="EE20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EF20" t="s">
         <v>243</v>
@@ -14218,10 +14221,10 @@
         <v>243</v>
       </c>
       <c r="EO20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EP20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EQ20" t="s">
         <v>243</v>
@@ -14233,7 +14236,7 @@
         <v>243</v>
       </c>
       <c r="ET20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="EU20" t="s">
         <v>243</v>
@@ -14296,97 +14299,97 @@
         <v>243</v>
       </c>
       <c r="FO20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FP20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FQ20" t="s">
         <v>243</v>
       </c>
       <c r="FR20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GP20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GQ20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GR20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GS20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GT20" t="s">
         <v>243</v>
@@ -14398,52 +14401,52 @@
         <v>243</v>
       </c>
       <c r="GW20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GX20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HD20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HE20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HF20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HH20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="HK20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="HL20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:220">
@@ -14574,13 +14577,13 @@
         <v>243</v>
       </c>
       <c r="AQ21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AR21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AS21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AT21" t="s">
         <v>243</v>
@@ -14778,28 +14781,28 @@
         <v>243</v>
       </c>
       <c r="DG21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DH21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DI21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DJ21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DK21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DM21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DN21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DO21" t="s">
         <v>243</v>
@@ -14868,10 +14871,10 @@
         <v>243</v>
       </c>
       <c r="EK21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EL21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="EM21" t="s">
         <v>243</v>
@@ -14964,82 +14967,82 @@
         <v>243</v>
       </c>
       <c r="FQ21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FR21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FS21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN21" t="s">
         <v>243</v>
       </c>
       <c r="GO21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GP21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GQ21" t="s">
         <v>243</v>
@@ -15060,52 +15063,52 @@
         <v>243</v>
       </c>
       <c r="GW21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GX21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HJ21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="HK21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="HL21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:220">
@@ -15449,10 +15452,10 @@
         <v>243</v>
       </c>
       <c r="DJ22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DK22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="DL22" t="s">
         <v>243</v>
@@ -15635,67 +15638,67 @@
         <v>243</v>
       </c>
       <c r="FT22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GD22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ22" t="s">
         <v>243</v>
       </c>
       <c r="GK22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GL22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GN22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GO22" t="s">
         <v>243</v>
@@ -15713,7 +15716,7 @@
         <v>243</v>
       </c>
       <c r="GT22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GU22" t="s">
         <v>243</v>
@@ -15731,13 +15734,13 @@
         <v>243</v>
       </c>
       <c r="GZ22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HA22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC22" t="s">
         <v>243</v>
@@ -15746,10 +15749,10 @@
         <v>243</v>
       </c>
       <c r="HE22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HF22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HG22" t="s">
         <v>243</v>
@@ -15761,13 +15764,13 @@
         <v>243</v>
       </c>
       <c r="HJ22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="HK22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="HL22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:220">
@@ -16258,16 +16261,16 @@
         <v>243</v>
       </c>
       <c r="FG23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FH23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FI23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FJ23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FK23" t="s">
         <v>243</v>
@@ -16294,142 +16297,142 @@
         <v>243</v>
       </c>
       <c r="FS23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FT23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="FU23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GO23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GP23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GQ23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GR23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GS23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GT23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GU23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GV23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GW23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GX23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GY23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GZ23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HA23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HF23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HG23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HH23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HI23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HJ23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="HK23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="HL23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:220">
@@ -16572,16 +16575,16 @@
         <v>243</v>
       </c>
       <c r="AU24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AV24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AW24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AX24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AY24" t="s">
         <v>243</v>
@@ -16647,7 +16650,7 @@
         <v>243</v>
       </c>
       <c r="BT24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="BU24" t="s">
         <v>243</v>
@@ -16683,22 +16686,22 @@
         <v>243</v>
       </c>
       <c r="CF24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="CG24" t="s">
         <v>243</v>
       </c>
       <c r="CH24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="CI24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="CJ24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="CK24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="CL24" t="s">
         <v>243</v>
@@ -16776,7 +16779,7 @@
         <v>243</v>
       </c>
       <c r="DK24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="DL24" t="s">
         <v>243</v>
@@ -16956,70 +16959,70 @@
         <v>243</v>
       </c>
       <c r="FS24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FT24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FU24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FV24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FW24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FX24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FY24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="FZ24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GA24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GB24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GC24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GD24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GE24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GF24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GG24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GH24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GI24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GJ24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GK24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GL24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GM24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="GN24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="GO24" t="s">
         <v>243</v>
@@ -17055,22 +17058,22 @@
         <v>243</v>
       </c>
       <c r="GZ24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HA24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HB24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HC24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HD24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="HE24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HF24" t="s">
         <v>243</v>
@@ -17085,13 +17088,13 @@
         <v>243</v>
       </c>
       <c r="HJ24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="HK24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="HL24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Maize_tukey_classification_matrix.xlsx
+++ b/outputs/Maize_tukey_classification_matrix.xlsx
@@ -745,7 +745,7 @@
     <t>West Pokot</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
